--- a/downloads/pricing-calculator/th.xlsx
+++ b/downloads/pricing-calculator/th.xlsx
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ฟรีจาก Lokalfleet · lokalfleet.com</t>
+          <t>ฟรีจาก RoveHQ · rovehq.io</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Lokalfleet บันทึกการจอง การชำระเงิน และค่าใช้จ่ายจริงของรถแต่ละคันให้อัตโนมัติ คุณจึงเทียบตัวเลขนี้กับผลจริงได้: lokalfleet.com</t>
+          <t>RoveHQ บันทึกการจอง การชำระเงิน และค่าใช้จ่ายจริงของรถแต่ละคันให้อัตโนมัติ คุณจึงเทียบตัวเลขนี้กับผลจริงได้: rovehq.io</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>ฟรีจาก Lokalfleet · lokalfleet.com</t>
+          <t>ฟรีจาก RoveHQ · rovehq.io</t>
         </is>
       </c>
     </row>
